--- a/raw/processedSamples/20260407_r9_DB_USDA-nasal-swabs_Nano-QuIC.xlsx
+++ b/raw/processedSamples/20260407_r9_DB_USDA-nasal-swabs_Nano-QuIC.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rowde002\Documents\Projects\usda-validation\raw\processedSamples\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{386CC09F-BE1C-4209-B6BA-1FBE7ECD3994}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27DC41DE-DCDC-4F6D-B178-D4FA00573C1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BD29825B-DB0E-4116-8155-7D362418E847}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{BD29825B-DB0E-4116-8155-7D362418E847}"/>
   </bookViews>
   <sheets>
     <sheet name="Microplate Cycle 1 (0 h)" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="607" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="705" uniqueCount="169">
   <si>
     <t>User: USER</t>
   </si>
@@ -541,6 +541,12 @@
   </si>
   <si>
     <t>S-1761</t>
+  </si>
+  <si>
+    <t>Dilutions</t>
+  </si>
+  <si>
+    <t>Sample IDs</t>
   </si>
 </sst>
 </file>
@@ -2267,7 +2273,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E181AA35-154E-4D9A-926E-D3EBB60CFF04}">
-  <dimension ref="A1:CT301"/>
+  <dimension ref="A1:CT303"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:98" x14ac:dyDescent="0.25">
@@ -88444,6 +88450,593 @@
         <v>4173</v>
       </c>
     </row>
+    <row r="302" spans="1:98" ht="30" x14ac:dyDescent="0.25">
+      <c r="A302" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B302" s="4"/>
+      <c r="C302" s="5">
+        <v>1000</v>
+      </c>
+      <c r="D302" s="5">
+        <v>100</v>
+      </c>
+      <c r="E302" s="5">
+        <v>100</v>
+      </c>
+      <c r="F302" s="5">
+        <v>100</v>
+      </c>
+      <c r="G302" s="5">
+        <v>100</v>
+      </c>
+      <c r="H302" s="5">
+        <v>100</v>
+      </c>
+      <c r="I302" s="5">
+        <v>100</v>
+      </c>
+      <c r="J302" s="5">
+        <v>100</v>
+      </c>
+      <c r="K302" s="5">
+        <v>100</v>
+      </c>
+      <c r="L302" s="5">
+        <v>100</v>
+      </c>
+      <c r="M302" s="5">
+        <v>100</v>
+      </c>
+      <c r="N302" s="5">
+        <v>100</v>
+      </c>
+      <c r="O302" s="5">
+        <v>1000</v>
+      </c>
+      <c r="P302" s="5">
+        <v>100</v>
+      </c>
+      <c r="Q302" s="5">
+        <v>100</v>
+      </c>
+      <c r="R302" s="5">
+        <v>100</v>
+      </c>
+      <c r="S302" s="5">
+        <v>100</v>
+      </c>
+      <c r="T302" s="5">
+        <v>100</v>
+      </c>
+      <c r="U302" s="5">
+        <v>100</v>
+      </c>
+      <c r="V302" s="5">
+        <v>100</v>
+      </c>
+      <c r="W302" s="5">
+        <v>100</v>
+      </c>
+      <c r="X302" s="5">
+        <v>100</v>
+      </c>
+      <c r="Y302" s="5">
+        <v>100</v>
+      </c>
+      <c r="Z302" s="5">
+        <v>100</v>
+      </c>
+      <c r="AA302" s="5">
+        <v>1000</v>
+      </c>
+      <c r="AB302" s="5">
+        <v>100</v>
+      </c>
+      <c r="AC302" s="5">
+        <v>100</v>
+      </c>
+      <c r="AD302" s="5">
+        <v>100</v>
+      </c>
+      <c r="AE302" s="5">
+        <v>100</v>
+      </c>
+      <c r="AF302" s="5">
+        <v>100</v>
+      </c>
+      <c r="AG302" s="5">
+        <v>100</v>
+      </c>
+      <c r="AH302" s="5">
+        <v>100</v>
+      </c>
+      <c r="AI302" s="5">
+        <v>100</v>
+      </c>
+      <c r="AJ302" s="5">
+        <v>100</v>
+      </c>
+      <c r="AK302" s="5">
+        <v>100</v>
+      </c>
+      <c r="AL302" s="5">
+        <v>100</v>
+      </c>
+      <c r="AM302" s="5">
+        <v>1000</v>
+      </c>
+      <c r="AN302" s="5">
+        <v>100</v>
+      </c>
+      <c r="AO302" s="5">
+        <v>100</v>
+      </c>
+      <c r="AP302" s="5">
+        <v>100</v>
+      </c>
+      <c r="AQ302" s="5">
+        <v>100</v>
+      </c>
+      <c r="AR302" s="5">
+        <v>100</v>
+      </c>
+      <c r="AS302" s="5">
+        <v>100</v>
+      </c>
+      <c r="AT302" s="5">
+        <v>100</v>
+      </c>
+      <c r="AU302" s="5">
+        <v>100</v>
+      </c>
+      <c r="AV302" s="5">
+        <v>100</v>
+      </c>
+      <c r="AW302" s="5">
+        <v>100</v>
+      </c>
+      <c r="AX302" s="5">
+        <v>100</v>
+      </c>
+      <c r="AY302" s="5">
+        <v>1000</v>
+      </c>
+      <c r="AZ302" s="5">
+        <v>1000</v>
+      </c>
+      <c r="BA302" s="5">
+        <v>1000</v>
+      </c>
+      <c r="BB302" s="5">
+        <v>1000</v>
+      </c>
+      <c r="BC302" s="5">
+        <v>1000</v>
+      </c>
+      <c r="BD302" s="5">
+        <v>1000</v>
+      </c>
+      <c r="BE302" s="5">
+        <v>1000</v>
+      </c>
+      <c r="BF302" s="5">
+        <v>1000</v>
+      </c>
+      <c r="BG302" s="5">
+        <v>1000</v>
+      </c>
+      <c r="BH302" s="5">
+        <v>1000</v>
+      </c>
+      <c r="BI302" s="5">
+        <v>1000</v>
+      </c>
+      <c r="BJ302" s="5">
+        <v>1000</v>
+      </c>
+      <c r="BK302" s="5">
+        <v>1000</v>
+      </c>
+      <c r="BL302" s="5">
+        <v>1000</v>
+      </c>
+      <c r="BM302" s="5">
+        <v>1000</v>
+      </c>
+      <c r="BN302" s="5">
+        <v>1000</v>
+      </c>
+      <c r="BO302" s="5">
+        <v>1000</v>
+      </c>
+      <c r="BP302" s="5">
+        <v>1000</v>
+      </c>
+      <c r="BQ302" s="5">
+        <v>1000</v>
+      </c>
+      <c r="BR302" s="5">
+        <v>1000</v>
+      </c>
+      <c r="BS302" s="5">
+        <v>1000</v>
+      </c>
+      <c r="BT302" s="5">
+        <v>1000</v>
+      </c>
+      <c r="BU302" s="5">
+        <v>1000</v>
+      </c>
+      <c r="BV302" s="5">
+        <v>1000</v>
+      </c>
+      <c r="BW302" s="5">
+        <v>1000</v>
+      </c>
+      <c r="BX302" s="5">
+        <v>1000</v>
+      </c>
+      <c r="BY302" s="5">
+        <v>1000</v>
+      </c>
+      <c r="BZ302" s="5">
+        <v>1000</v>
+      </c>
+      <c r="CA302" s="5">
+        <v>1000</v>
+      </c>
+      <c r="CB302" s="5">
+        <v>1000</v>
+      </c>
+      <c r="CC302" s="5">
+        <v>1000</v>
+      </c>
+      <c r="CD302" s="5">
+        <v>1000</v>
+      </c>
+      <c r="CE302" s="5">
+        <v>1000</v>
+      </c>
+      <c r="CF302" s="5">
+        <v>1000</v>
+      </c>
+      <c r="CG302" s="5">
+        <v>1000</v>
+      </c>
+      <c r="CH302" s="5">
+        <v>1000</v>
+      </c>
+      <c r="CI302" s="5">
+        <v>1000</v>
+      </c>
+      <c r="CJ302" s="5">
+        <v>1000</v>
+      </c>
+      <c r="CK302" s="5">
+        <v>1000</v>
+      </c>
+      <c r="CL302" s="5">
+        <v>1000</v>
+      </c>
+      <c r="CM302" s="5">
+        <v>1000</v>
+      </c>
+      <c r="CN302" s="5">
+        <v>1000</v>
+      </c>
+      <c r="CO302" s="5">
+        <v>1000</v>
+      </c>
+      <c r="CP302" s="5">
+        <v>1000</v>
+      </c>
+      <c r="CQ302" s="5">
+        <v>1000</v>
+      </c>
+      <c r="CR302" s="5">
+        <v>1000</v>
+      </c>
+      <c r="CS302" s="5">
+        <v>1000</v>
+      </c>
+      <c r="CT302" s="6">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="303" spans="1:98" ht="30" x14ac:dyDescent="0.25">
+      <c r="A303" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C303" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="D303" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="E303" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="F303" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="G303" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="H303" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="I303" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="J303" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="K303" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="L303" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="M303" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="N303" s="16" t="s">
+        <v>155</v>
+      </c>
+      <c r="O303" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="P303" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="Q303" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="R303" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="S303" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="T303" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="U303" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="V303" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="W303" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="X303" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="Y303" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="Z303" s="16" t="s">
+        <v>155</v>
+      </c>
+      <c r="AA303" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="AB303" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="AC303" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="AD303" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="AE303" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="AF303" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="AG303" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="AH303" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="AI303" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="AJ303" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="AK303" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="AL303" s="16" t="s">
+        <v>155</v>
+      </c>
+      <c r="AM303" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="AN303" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="AO303" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="AP303" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="AQ303" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="AR303" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="AS303" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="AT303" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="AU303" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="AV303" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="AW303" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="AX303" s="16" t="s">
+        <v>155</v>
+      </c>
+      <c r="AY303" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="AZ303" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="BA303" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="BB303" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="BC303" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="BD303" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="BE303" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="BF303" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="BG303" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="BH303" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="BI303" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="BJ303" s="16" t="s">
+        <v>166</v>
+      </c>
+      <c r="BK303" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="BL303" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="BM303" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="BN303" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="BO303" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="BP303" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="BQ303" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="BR303" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="BS303" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="BT303" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="BU303" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="BV303" s="16" t="s">
+        <v>166</v>
+      </c>
+      <c r="BW303" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="BX303" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="BY303" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="BZ303" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="CA303" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="CB303" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="CC303" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="CD303" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="CE303" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="CF303" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="CG303" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="CH303" s="16" t="s">
+        <v>166</v>
+      </c>
+      <c r="CI303" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="CJ303" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="CK303" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="CL303" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="CM303" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="CN303" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="CO303" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="CP303" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="CQ303" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="CR303" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="CS303" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="CT303" s="16" t="s">
+        <v>166</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
